--- a/filer/14194711_dfds.xlsx
+++ b/filer/14194711_dfds.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3329,49 +3329,49 @@
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B61" s="11">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B61" s="8">
         <f>'balance_raw'!$B$38</f>
         <v/>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="8">
         <f>'balance_raw'!$C$38</f>
         <v/>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="8">
         <f>'balance_raw'!$D$38</f>
         <v/>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="8">
         <f>'balance_raw'!$E$38</f>
         <v/>
       </c>
-      <c r="F61" s="11">
+      <c r="F61" s="8">
         <f>'balance_raw'!$F$38</f>
         <v/>
       </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" s="12">
+      <c r="H61" s="9">
         <f>IFERROR(B61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="I61" s="12">
+      <c r="I61" s="9">
         <f>IFERROR(C61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="J61" s="12">
+      <c r="J61" s="9">
         <f>IFERROR(D61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="K61" s="12">
+      <c r="K61" s="9">
         <f>IFERROR(E61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="L61" s="12">
+      <c r="L61" s="9">
         <f>IFERROR(F61/$B$61*100,"")</f>
         <v/>
       </c>
@@ -3379,7 +3379,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Langfristede lån</t>
         </is>
       </c>
       <c r="B62" s="5">
@@ -3427,7 +3427,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
       <c r="B63" s="8">
@@ -3475,7 +3475,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
+          <t>Anden gæld (langfristet)</t>
         </is>
       </c>
       <c r="B64" s="5">
@@ -3521,49 +3521,49 @@
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B65" s="8">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B65" s="11">
         <f>'balance_raw'!$B$42</f>
         <v/>
       </c>
-      <c r="C65" s="8">
+      <c r="C65" s="11">
         <f>'balance_raw'!$C$42</f>
         <v/>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="11">
         <f>'balance_raw'!$D$42</f>
         <v/>
       </c>
-      <c r="E65" s="8">
+      <c r="E65" s="11">
         <f>'balance_raw'!$E$42</f>
         <v/>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="11">
         <f>'balance_raw'!$F$42</f>
         <v/>
       </c>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" s="9">
+      <c r="H65" s="12">
         <f>IFERROR(B65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="I65" s="9">
+      <c r="I65" s="12">
         <f>IFERROR(C65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="J65" s="9">
+      <c r="J65" s="12">
         <f>IFERROR(D65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="K65" s="9">
+      <c r="K65" s="12">
         <f>IFERROR(E65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="L65" s="9">
+      <c r="L65" s="12">
         <f>IFERROR(F65/$B$65*100,"")</f>
         <v/>
       </c>
@@ -3571,7 +3571,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B66" s="5">
@@ -3619,7 +3619,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B67" s="8">
@@ -3667,7 +3667,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B68" s="5">
@@ -3715,7 +3715,7 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B69" s="8">
@@ -3763,7 +3763,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B70" s="5">
@@ -3811,7 +3811,7 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B71" s="8">
@@ -3859,7 +3859,7 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B72" s="5">
@@ -3905,263 +3905,337 @@
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="10" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B73" s="8">
+        <f>'balance_raw'!$B$50</f>
+        <v/>
+      </c>
+      <c r="C73" s="8">
+        <f>'balance_raw'!$C$50</f>
+        <v/>
+      </c>
+      <c r="D73" s="8">
+        <f>'balance_raw'!$D$50</f>
+        <v/>
+      </c>
+      <c r="E73" s="8">
+        <f>'balance_raw'!$E$50</f>
+        <v/>
+      </c>
+      <c r="F73" s="8">
+        <f>'balance_raw'!$F$50</f>
+        <v/>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" s="9">
+        <f>IFERROR(B73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="I73" s="9">
+        <f>IFERROR(C73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="J73" s="9">
+        <f>IFERROR(D73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="K73" s="9">
+        <f>IFERROR(E73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="L73" s="9">
+        <f>IFERROR(F73/$B$73*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B74" s="5">
+        <f>'balance_raw'!$B$51</f>
+        <v/>
+      </c>
+      <c r="C74" s="5">
+        <f>'balance_raw'!$C$51</f>
+        <v/>
+      </c>
+      <c r="D74" s="5">
+        <f>'balance_raw'!$D$51</f>
+        <v/>
+      </c>
+      <c r="E74" s="5">
+        <f>'balance_raw'!$E$51</f>
+        <v/>
+      </c>
+      <c r="F74" s="5">
+        <f>'balance_raw'!$F$51</f>
+        <v/>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" s="6">
+        <f>IFERROR(B74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="I74" s="6">
+        <f>IFERROR(C74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="J74" s="6">
+        <f>IFERROR(D74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="K74" s="6">
+        <f>IFERROR(E74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="L74" s="6">
+        <f>IFERROR(F74/$B$74*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B75" s="8">
+        <f>'balance_raw'!$B$52</f>
+        <v/>
+      </c>
+      <c r="C75" s="8">
+        <f>'balance_raw'!$C$52</f>
+        <v/>
+      </c>
+      <c r="D75" s="8">
+        <f>'balance_raw'!$D$52</f>
+        <v/>
+      </c>
+      <c r="E75" s="8">
+        <f>'balance_raw'!$E$52</f>
+        <v/>
+      </c>
+      <c r="F75" s="8">
+        <f>'balance_raw'!$F$52</f>
+        <v/>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" s="9">
+        <f>IFERROR(B75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="I75" s="9">
+        <f>IFERROR(C75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="J75" s="9">
+        <f>IFERROR(D75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="K75" s="9">
+        <f>IFERROR(E75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="L75" s="9">
+        <f>IFERROR(F75/$B$75*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B76" s="5">
+        <f>'balance_raw'!$B$53</f>
+        <v/>
+      </c>
+      <c r="C76" s="5">
+        <f>'balance_raw'!$C$53</f>
+        <v/>
+      </c>
+      <c r="D76" s="5">
+        <f>'balance_raw'!$D$53</f>
+        <v/>
+      </c>
+      <c r="E76" s="5">
+        <f>'balance_raw'!$E$53</f>
+        <v/>
+      </c>
+      <c r="F76" s="5">
+        <f>'balance_raw'!$F$53</f>
+        <v/>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" s="6">
+        <f>IFERROR(B76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="I76" s="6">
+        <f>IFERROR(C76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="J76" s="6">
+        <f>IFERROR(D76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="K76" s="6">
+        <f>IFERROR(E76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="L76" s="6">
+        <f>IFERROR(F76/$B$76*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B73" s="11">
-        <f>'balance_raw'!$B$50</f>
-        <v/>
-      </c>
-      <c r="C73" s="11">
-        <f>'balance_raw'!$C$50</f>
-        <v/>
-      </c>
-      <c r="D73" s="11">
-        <f>'balance_raw'!$D$50</f>
-        <v/>
-      </c>
-      <c r="E73" s="11">
-        <f>'balance_raw'!$E$50</f>
-        <v/>
-      </c>
-      <c r="F73" s="11">
-        <f>'balance_raw'!$F$50</f>
-        <v/>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" s="12">
-        <f>IFERROR(B73/$B$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="I73" s="12">
-        <f>IFERROR(C73/$B$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="J73" s="12">
-        <f>IFERROR(D73/$B$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="K73" s="12">
-        <f>IFERROR(E73/$B$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="L73" s="12">
-        <f>IFERROR(F73/$B$73*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="B77" s="11">
+        <f>'balance_raw'!$B$54</f>
+        <v/>
+      </c>
+      <c r="C77" s="11">
+        <f>'balance_raw'!$C$54</f>
+        <v/>
+      </c>
+      <c r="D77" s="11">
+        <f>'balance_raw'!$D$54</f>
+        <v/>
+      </c>
+      <c r="E77" s="11">
+        <f>'balance_raw'!$E$54</f>
+        <v/>
+      </c>
+      <c r="F77" s="11">
+        <f>'balance_raw'!$F$54</f>
+        <v/>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" s="12">
+        <f>IFERROR(B77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="I77" s="12">
+        <f>IFERROR(C77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="J77" s="12">
+        <f>IFERROR(D77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="K77" s="12">
+        <f>IFERROR(E77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="L77" s="12">
+        <f>IFERROR(F77/$B$77*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B74" s="11">
-        <f>'balance_raw'!$B$51</f>
-        <v/>
-      </c>
-      <c r="C74" s="11">
-        <f>'balance_raw'!$C$51</f>
-        <v/>
-      </c>
-      <c r="D74" s="11">
-        <f>'balance_raw'!$D$51</f>
-        <v/>
-      </c>
-      <c r="E74" s="11">
-        <f>'balance_raw'!$E$51</f>
-        <v/>
-      </c>
-      <c r="F74" s="11">
-        <f>'balance_raw'!$F$51</f>
-        <v/>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" s="12">
-        <f>IFERROR(B74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="I74" s="12">
-        <f>IFERROR(C74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="J74" s="12">
-        <f>IFERROR(D74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="K74" s="12">
-        <f>IFERROR(E74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="L74" s="12">
-        <f>IFERROR(F74/$B$74*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
+      <c r="B78" s="11">
+        <f>'balance_raw'!$B$55</f>
+        <v/>
+      </c>
+      <c r="C78" s="11">
+        <f>'balance_raw'!$C$55</f>
+        <v/>
+      </c>
+      <c r="D78" s="11">
+        <f>'balance_raw'!$D$55</f>
+        <v/>
+      </c>
+      <c r="E78" s="11">
+        <f>'balance_raw'!$E$55</f>
+        <v/>
+      </c>
+      <c r="F78" s="11">
+        <f>'balance_raw'!$F$55</f>
+        <v/>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" s="12">
+        <f>IFERROR(B78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="I78" s="12">
+        <f>IFERROR(C78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="J78" s="12">
+        <f>IFERROR(D78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="K78" s="12">
+        <f>IFERROR(E78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="L78" s="12">
+        <f>IFERROR(F78/$B$78*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B75" s="11">
-        <f>'balance_raw'!$B$52</f>
-        <v/>
-      </c>
-      <c r="C75" s="11">
-        <f>'balance_raw'!$C$52</f>
-        <v/>
-      </c>
-      <c r="D75" s="11">
-        <f>'balance_raw'!$D$52</f>
-        <v/>
-      </c>
-      <c r="E75" s="11">
-        <f>'balance_raw'!$E$52</f>
-        <v/>
-      </c>
-      <c r="F75" s="11">
-        <f>'balance_raw'!$F$52</f>
-        <v/>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" s="12">
-        <f>IFERROR(B75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="I75" s="12">
-        <f>IFERROR(C75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="J75" s="12">
-        <f>IFERROR(D75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="K75" s="12">
-        <f>IFERROR(E75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="L75" s="12">
-        <f>IFERROR(F75/$B$75*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>NØGLEOPLYSNINGER</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D77" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Gns. antal medarbejdere</t>
-        </is>
-      </c>
-      <c r="B78" s="5">
-        <f>'res_raw'!$B$19</f>
-        <v/>
-      </c>
-      <c r="C78" s="5">
-        <f>'res_raw'!$C$19</f>
-        <v/>
-      </c>
-      <c r="D78" s="5">
-        <f>'res_raw'!$D$19</f>
-        <v/>
-      </c>
-      <c r="E78" s="5">
-        <f>'res_raw'!$E$19</f>
-        <v/>
-      </c>
-      <c r="F78" s="5">
-        <f>'res_raw'!$F$19</f>
-        <v/>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" s="6">
-        <f>IFERROR(B78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="I78" s="6">
-        <f>IFERROR(C78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="J78" s="6">
-        <f>IFERROR(D78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="K78" s="6">
-        <f>IFERROR(E78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="L78" s="6">
-        <f>IFERROR(F78/$B$78*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B79" s="8">
-        <f>'res_raw'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C79" s="8">
-        <f>'res_raw'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D79" s="8">
-        <f>'res_raw'!$D$20</f>
-        <v/>
-      </c>
-      <c r="E79" s="8">
-        <f>'res_raw'!$E$20</f>
-        <v/>
-      </c>
-      <c r="F79" s="8">
-        <f>'res_raw'!$F$20</f>
+      <c r="B79" s="11">
+        <f>'balance_raw'!$B$56</f>
+        <v/>
+      </c>
+      <c r="C79" s="11">
+        <f>'balance_raw'!$C$56</f>
+        <v/>
+      </c>
+      <c r="D79" s="11">
+        <f>'balance_raw'!$D$56</f>
+        <v/>
+      </c>
+      <c r="E79" s="11">
+        <f>'balance_raw'!$E$56</f>
+        <v/>
+      </c>
+      <c r="F79" s="11">
+        <f>'balance_raw'!$F$56</f>
         <v/>
       </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" s="9">
+      <c r="H79" s="12">
         <f>IFERROR(B79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="I79" s="9">
+      <c r="I79" s="12">
         <f>IFERROR(C79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="J79" s="9">
+      <c r="J79" s="12">
         <f>IFERROR(D79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="K79" s="9">
+      <c r="K79" s="12">
         <f>IFERROR(E79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="L79" s="9">
+      <c r="L79" s="12">
         <f>IFERROR(F79/$B$79*100,"")</f>
         <v/>
       </c>
@@ -4169,7 +4243,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>NØGLETAL</t>
+          <t>NØGLEOPLYSNINGER</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
@@ -4191,297 +4265,415 @@
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B82" s="13">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="C82" s="13">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="13">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="13">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="F82" s="13">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$49*100,"")</f>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B82" s="5">
+        <f>'res_raw'!$B$19</f>
+        <v/>
+      </c>
+      <c r="C82" s="5">
+        <f>'res_raw'!$C$19</f>
+        <v/>
+      </c>
+      <c r="D82" s="5">
+        <f>'res_raw'!$D$19</f>
+        <v/>
+      </c>
+      <c r="E82" s="5">
+        <f>'res_raw'!$E$19</f>
+        <v/>
+      </c>
+      <c r="F82" s="5">
+        <f>'res_raw'!$F$19</f>
+        <v/>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" s="6">
+        <f>IFERROR(B82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="I82" s="6">
+        <f>IFERROR(C82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="J82" s="6">
+        <f>IFERROR(D82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="K82" s="6">
+        <f>IFERROR(E82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="L82" s="6">
+        <f>IFERROR(F82/$B$82*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B83" s="14">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="C83" s="14">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="14">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="14">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="F83" s="14">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B84" s="13">
-        <f>IFERROR($B$4/$B$49,"")</f>
-        <v/>
-      </c>
-      <c r="C84" s="13">
-        <f>IFERROR($C$4/$C$49,"")</f>
-        <v/>
-      </c>
-      <c r="D84" s="13">
-        <f>IFERROR($D$4/$D$49,"")</f>
-        <v/>
-      </c>
-      <c r="E84" s="13">
-        <f>IFERROR($E$4/$E$49,"")</f>
-        <v/>
-      </c>
-      <c r="F84" s="13">
-        <f>IFERROR($F$4/$F$49,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B85" s="14">
-        <f>IFERROR($B$18/$B$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="C85" s="14">
-        <f>IFERROR($C$18/$C$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="D85" s="14">
-        <f>IFERROR($D$18/$D$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="E85" s="14">
-        <f>IFERROR($E$18/$E$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="F85" s="14">
-        <f>IFERROR($F$18/$F$58*100,"")</f>
-        <v/>
+          <t>Investering i materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B83" s="8">
+        <f>'res_raw'!$B$20</f>
+        <v/>
+      </c>
+      <c r="C83" s="8">
+        <f>'res_raw'!$C$20</f>
+        <v/>
+      </c>
+      <c r="D83" s="8">
+        <f>'res_raw'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E83" s="8">
+        <f>'res_raw'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F83" s="8">
+        <f>'res_raw'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" s="9">
+        <f>IFERROR(B83/$B$83*100,"")</f>
+        <v/>
+      </c>
+      <c r="I83" s="9">
+        <f>IFERROR(C83/$B$83*100,"")</f>
+        <v/>
+      </c>
+      <c r="J83" s="9">
+        <f>IFERROR(D83/$B$83*100,"")</f>
+        <v/>
+      </c>
+      <c r="K83" s="9">
+        <f>IFERROR(E83/$B$83*100,"")</f>
+        <v/>
+      </c>
+      <c r="L83" s="9">
+        <f>IFERROR(F83/$B$83*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>NØGLETAL</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
+          <t>Afkastningsgrad, %</t>
         </is>
       </c>
       <c r="B86" s="13">
-        <f>IFERROR($B$16/($B$75-$B$58)*100,"")</f>
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$49*100,"")</f>
         <v/>
       </c>
       <c r="C86" s="13">
-        <f>IFERROR($C$16/($C$75-$C$58)*100,"")</f>
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$49*100,"")</f>
         <v/>
       </c>
       <c r="D86" s="13">
-        <f>IFERROR($D$16/($D$75-$D$58)*100,"")</f>
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$49*100,"")</f>
         <v/>
       </c>
       <c r="E86" s="13">
-        <f>IFERROR($E$16/($E$75-$E$58)*100,"")</f>
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$49*100,"")</f>
         <v/>
       </c>
       <c r="F86" s="13">
-        <f>IFERROR($F$16/($F$75-$F$58)*100,"")</f>
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$49*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
+          <t>Overskudsgrad, %</t>
         </is>
       </c>
       <c r="B87" s="14">
-        <f>IFERROR($B$58/$B$49*100,"")</f>
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
         <v/>
       </c>
       <c r="C87" s="14">
-        <f>IFERROR($C$58/$C$49*100,"")</f>
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
         <v/>
       </c>
       <c r="D87" s="14">
-        <f>IFERROR($D$58/$D$49*100,"")</f>
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
         <v/>
       </c>
       <c r="E87" s="14">
-        <f>IFERROR($E$58/$E$49*100,"")</f>
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
         <v/>
       </c>
       <c r="F87" s="14">
-        <f>IFERROR($F$58/$F$49*100,"")</f>
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Gearing</t>
+          <t>Aktivernes omsætningshastighed, gange</t>
         </is>
       </c>
       <c r="B88" s="13">
-        <f>IFERROR(($B$75-$B$58)/$B$58,"")</f>
+        <f>IFERROR($B$4/$B$49,"")</f>
         <v/>
       </c>
       <c r="C88" s="13">
-        <f>IFERROR(($C$75-$C$58)/$C$58,"")</f>
+        <f>IFERROR($C$4/$C$49,"")</f>
         <v/>
       </c>
       <c r="D88" s="13">
-        <f>IFERROR(($D$75-$D$58)/$D$58,"")</f>
+        <f>IFERROR($D$4/$D$49,"")</f>
         <v/>
       </c>
       <c r="E88" s="13">
-        <f>IFERROR(($E$75-$E$58)/$E$58,"")</f>
+        <f>IFERROR($E$4/$E$49,"")</f>
         <v/>
       </c>
       <c r="F88" s="13">
-        <f>IFERROR(($F$75-$F$58)/$F$58,"")</f>
+        <f>IFERROR($F$4/$F$49,"")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Likviditetsgrad, %</t>
+          <t>Egenkapitalens forrentning, %</t>
         </is>
       </c>
       <c r="B89" s="14">
-        <f>IFERROR($B$48/$B$73*100,"")</f>
+        <f>IFERROR($B$18/$B$58*100,"")</f>
         <v/>
       </c>
       <c r="C89" s="14">
-        <f>IFERROR($C$48/$C$73*100,"")</f>
+        <f>IFERROR($C$18/$C$58*100,"")</f>
         <v/>
       </c>
       <c r="D89" s="14">
-        <f>IFERROR($D$48/$D$73*100,"")</f>
+        <f>IFERROR($D$18/$D$58*100,"")</f>
         <v/>
       </c>
       <c r="E89" s="14">
-        <f>IFERROR($E$48/$E$73*100,"")</f>
+        <f>IFERROR($E$18/$E$58*100,"")</f>
         <v/>
       </c>
       <c r="F89" s="14">
-        <f>IFERROR($F$48/$F$73*100,"")</f>
+        <f>IFERROR($F$18/$F$58*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Rentemarginal, %</t>
+          <t>Gældsrente, %</t>
         </is>
       </c>
       <c r="B90" s="13">
-        <f>IFERROR(B82-B86,"")</f>
+        <f>IFERROR($B$16/($B$79-$B$58)*100,"")</f>
         <v/>
       </c>
       <c r="C90" s="13">
-        <f>IFERROR(C82-C86,"")</f>
+        <f>IFERROR($C$16/($C$79-$C$58)*100,"")</f>
         <v/>
       </c>
       <c r="D90" s="13">
-        <f>IFERROR(D82-D86,"")</f>
+        <f>IFERROR($D$16/($D$79-$D$58)*100,"")</f>
         <v/>
       </c>
       <c r="E90" s="13">
-        <f>IFERROR(E82-E86,"")</f>
+        <f>IFERROR($E$16/($E$79-$E$58)*100,"")</f>
         <v/>
       </c>
       <c r="F90" s="13">
-        <f>IFERROR(F82-F86,"")</f>
+        <f>IFERROR($F$16/($F$79-$F$58)*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Gældsandel, %</t>
+          <t>Soliditetsgrad, %</t>
         </is>
       </c>
       <c r="B91" s="14">
-        <f>IFERROR(($B$75-$B$58)/$B$49*100,"")</f>
+        <f>IFERROR($B$58/$B$49*100,"")</f>
         <v/>
       </c>
       <c r="C91" s="14">
-        <f>IFERROR(($C$75-$C$58)/$C$49*100,"")</f>
+        <f>IFERROR($C$58/$C$49*100,"")</f>
         <v/>
       </c>
       <c r="D91" s="14">
-        <f>IFERROR(($D$75-$D$58)/$D$49*100,"")</f>
+        <f>IFERROR($D$58/$D$49*100,"")</f>
         <v/>
       </c>
       <c r="E91" s="14">
-        <f>IFERROR(($E$75-$E$58)/$E$49*100,"")</f>
+        <f>IFERROR($E$58/$E$49*100,"")</f>
         <v/>
       </c>
       <c r="F91" s="14">
-        <f>IFERROR(($F$75-$F$58)/$F$49*100,"")</f>
+        <f>IFERROR($F$58/$F$49*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
+          <t>Gearing</t>
+        </is>
+      </c>
+      <c r="B92" s="13">
+        <f>IFERROR(($B$79-$B$58)/$B$58,"")</f>
+        <v/>
+      </c>
+      <c r="C92" s="13">
+        <f>IFERROR(($C$79-$C$58)/$C$58,"")</f>
+        <v/>
+      </c>
+      <c r="D92" s="13">
+        <f>IFERROR(($D$79-$D$58)/$D$58,"")</f>
+        <v/>
+      </c>
+      <c r="E92" s="13">
+        <f>IFERROR(($E$79-$E$58)/$E$58,"")</f>
+        <v/>
+      </c>
+      <c r="F92" s="13">
+        <f>IFERROR(($F$79-$F$58)/$F$58,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Likviditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B93" s="14">
+        <f>IFERROR($B$48/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="C93" s="14">
+        <f>IFERROR($C$48/$C$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="D93" s="14">
+        <f>IFERROR($D$48/$D$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="E93" s="14">
+        <f>IFERROR($E$48/$E$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="F93" s="14">
+        <f>IFERROR($F$48/$F$77*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Rentemarginal, %</t>
+        </is>
+      </c>
+      <c r="B94" s="13">
+        <f>IFERROR(B86-B90,"")</f>
+        <v/>
+      </c>
+      <c r="C94" s="13">
+        <f>IFERROR(C86-C90,"")</f>
+        <v/>
+      </c>
+      <c r="D94" s="13">
+        <f>IFERROR(D86-D90,"")</f>
+        <v/>
+      </c>
+      <c r="E94" s="13">
+        <f>IFERROR(E86-E90,"")</f>
+        <v/>
+      </c>
+      <c r="F94" s="13">
+        <f>IFERROR(F86-F90,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B95" s="14">
+        <f>IFERROR(($B$79-$B$58)/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="C95" s="14">
+        <f>IFERROR(($C$79-$C$58)/$C$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="D95" s="14">
+        <f>IFERROR(($D$79-$D$58)/$D$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="E95" s="14">
+        <f>IFERROR(($E$79-$E$58)/$E$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="F95" s="14">
+        <f>IFERROR(($F$79-$F$58)/$F$49*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
           <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
-      <c r="B92" s="13">
-        <f>IFERROR($B$36/($B$58+$B$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C92" s="13">
-        <f>IFERROR($C$36/($C$58+$C$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D92" s="13">
-        <f>IFERROR($D$36/($D$58+$D$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E92" s="13">
-        <f>IFERROR($E$36/($E$58+$E$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F92" s="13">
-        <f>IFERROR($F$36/($F$58+$F$61)*100,"")</f>
+      <c r="B96" s="13">
+        <f>IFERROR($B$36/($B$58+$B$65)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C96" s="13">
+        <f>IFERROR($C$36/($C$58+$C$65)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D96" s="13">
+        <f>IFERROR($D$36/($D$58+$D$65)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E96" s="13">
+        <f>IFERROR($E$36/($E$58+$E$65)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F96" s="13">
+        <f>IFERROR($F$36/($F$58+$F$65)*100,"")</f>
         <v/>
       </c>
     </row>
@@ -4557,12 +4749,20 @@
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
+      <c r="B3" s="16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>21000</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>113000</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>43000</v>
+      </c>
       <c r="F3" s="16" t="n">
-        <v>119000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="4">
@@ -4875,7 +5075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -5559,31 +5759,21 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n">
-        <v>11825000</v>
-      </c>
-      <c r="C38" s="16" t="n">
-        <v>12397000</v>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>13602000</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>17113000</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>14477000</v>
-      </c>
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Langfristede lån</t>
         </is>
       </c>
       <c r="B39" s="16" t="n"/>
@@ -5595,7 +5785,7 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
       <c r="B40" s="16" t="n"/>
@@ -5607,63 +5797,63 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
+          <t>Anden gæld (langfristet)</t>
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>2511000</v>
+        <v>6000</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>3137000</v>
+        <v>8000</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>1627000</v>
+        <v>43000</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>1621000</v>
+        <v>74000</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>2539000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n">
+        <v>11825000</v>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>12397000</v>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>13602000</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>17113000</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>14477000</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
-        <v>3119000</v>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>3661000</v>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>3461000</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>3984000</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>3753000</v>
-      </c>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B44" s="16" t="n"/>
@@ -5675,19 +5865,29 @@
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="n">
+        <v>2511000</v>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>3137000</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>1627000</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>1621000</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>2539000</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B46" s="16" t="n"/>
@@ -5699,41 +5899,41 @@
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="n">
+        <v>3119000</v>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>3661000</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>3461000</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>3984000</v>
+      </c>
+      <c r="F47" s="16" t="n">
+        <v>3753000</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>730000</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>768000</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>904000</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>1160000</v>
-      </c>
-      <c r="F48" s="16" t="n">
-        <v>1135000</v>
-      </c>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="16" t="n"/>
+      <c r="F48" s="16" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B49" s="16" t="n"/>
@@ -5743,68 +5943,126 @@
       <c r="F49" s="16" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="n"/>
+      <c r="C50" s="16" t="n"/>
+      <c r="D50" s="16" t="n"/>
+      <c r="E50" s="16" t="n"/>
+      <c r="F50" s="16" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="n"/>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="n"/>
+      <c r="E51" s="16" t="n"/>
+      <c r="F51" s="16" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="n">
+        <v>730000</v>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>768000</v>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>904000</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>1160000</v>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>1135000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="n"/>
+      <c r="C53" s="16" t="n"/>
+      <c r="D53" s="16" t="n"/>
+      <c r="E53" s="16" t="n"/>
+      <c r="F53" s="16" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
+      <c r="B54" s="16" t="n">
         <v>6778000</v>
       </c>
-      <c r="C50" s="16" t="n">
+      <c r="C54" s="16" t="n">
         <v>8053000</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D54" s="16" t="n">
         <v>6491000</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E54" s="16" t="n">
         <v>7521000</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="F54" s="16" t="n">
         <v>8421000</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
+      <c r="B55" s="16" t="n">
         <v>19167000</v>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C55" s="16" t="n">
         <v>20949000</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D55" s="16" t="n">
         <v>20715000</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E55" s="16" t="n">
         <v>25392000</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="F55" s="16" t="n">
         <v>23670000</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="17" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
+      <c r="B56" s="16" t="n">
         <v>30721000</v>
       </c>
-      <c r="C52" s="16" t="n">
+      <c r="C56" s="16" t="n">
         <v>34084000</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D56" s="16" t="n">
         <v>34647000</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="E56" s="16" t="n">
         <v>39281000</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="F56" s="16" t="n">
         <v>37117000</v>
       </c>
     </row>
@@ -6285,15 +6543,15 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>'balance_raw'!$F$52-'balance_raw'!$F$35</f>
+        <f>'balance_raw'!$F$56-'balance_raw'!$F$35</f>
         <v/>
       </c>
       <c r="C24" s="24">
-        <f>'balance_raw'!$E$52-'balance_raw'!$E$35</f>
+        <f>'balance_raw'!$E$56-'balance_raw'!$E$35</f>
         <v/>
       </c>
       <c r="D24" s="24">
-        <f>'balance_raw'!$D$52-'balance_raw'!$D$35</f>
+        <f>'balance_raw'!$D$56-'balance_raw'!$D$35</f>
         <v/>
       </c>
       <c r="F24" s="25" t="inlineStr">
@@ -6399,15 +6657,15 @@
         </is>
       </c>
       <c r="B30" s="24">
-        <f>'balance_raw'!$F$50</f>
+        <f>'balance_raw'!$F$54</f>
         <v/>
       </c>
       <c r="C30" s="24">
-        <f>'balance_raw'!$E$50</f>
+        <f>'balance_raw'!$E$54</f>
         <v/>
       </c>
       <c r="D30" s="24">
-        <f>'balance_raw'!$D$50</f>
+        <f>'balance_raw'!$D$54</f>
         <v/>
       </c>
       <c r="F30" s="25" t="inlineStr">
@@ -6915,15 +7173,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw'!$F$52="","—",IF(ABS(B25-'balance_raw'!$F$52)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw'!$F$52,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$F$56="","—",IF(ABS(B25-'balance_raw'!$F$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw'!$F$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw'!$E$52="","—",IF(ABS(C25-'balance_raw'!$E$52)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw'!$E$52,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$E$56="","—",IF(ABS(C25-'balance_raw'!$E$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw'!$E$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw'!$D$52="","—",IF(ABS(D25-'balance_raw'!$D$52)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw'!$D$52,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$D$56="","—",IF(ABS(D25-'balance_raw'!$D$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw'!$D$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -7042,7 +7300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7188,28 +7446,24 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialAssets</t>
+          <t>ifrs-full:DividendsRecognisedAsDistributionsToNoncontrollingInterests</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialAssets</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>22000</v>
-      </c>
+          <t>ifrs-full:DividendsRecognisedAsDistributionsToNoncontrollingInterests</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n">
-        <v>48000</v>
-      </c>
-      <c r="F5" s="35" t="n">
-        <v>20000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="35" t="n"/>
       <c r="G5" s="35" t="n">
-        <v>51000</v>
+        <v>0</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7225,29 +7479,23 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialLiabilities</t>
+          <t>ifrs-full:DividendsRecognisedAsDistributionsToOwnersPerShare</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialLiabilities</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n">
-        <v>77000</v>
-      </c>
+          <t>ifrs-full:DividendsRecognisedAsDistributionsToOwnersPerShare</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n"/>
       <c r="E6" s="38" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>52000</v>
-      </c>
-      <c r="G6" s="38" t="n">
-        <v>69000</v>
-      </c>
-      <c r="H6" s="38" t="n">
-        <v>81000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G6" s="38" t="n"/>
+      <c r="H6" s="38" t="n"/>
       <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7262,25 +7510,27 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:DividendsRecognisedAsDistributionsToNoncontrollingInterests</t>
+          <t>ifrs-full:NoncurrentPrepayments</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:DividendsRecognisedAsDistributionsToNoncontrollingInterests</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n"/>
+          <t>ifrs-full:NoncurrentPrepayments</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>222000</v>
+      </c>
       <c r="E7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="35" t="n"/>
+        <v>124000</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>1000</v>
+      </c>
       <c r="G7" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="35" t="n">
-        <v>0</v>
-      </c>
+      <c r="H7" s="35" t="n"/>
       <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7295,23 +7545,29 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:DividendsRecognisedAsDistributionsToOwnersPerShare</t>
+          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsFinancingActivities</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:DividendsRecognisedAsDistributionsToOwnersPerShare</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n"/>
+          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsFinancingActivities</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" s="38" t="n">
-        <v>0</v>
+        <v>-33000</v>
       </c>
       <c r="F8" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="38" t="n"/>
-      <c r="H8" s="38" t="n"/>
+        <v>-8000</v>
+      </c>
+      <c r="G8" s="38" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>41000</v>
+      </c>
       <c r="I8" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7326,28 +7582,28 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:GainsLossesOnDisposalsOfNoncurrentAssets</t>
+          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsInvestingActivities</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:GainsLossesOnDisposalsOfNoncurrentAssets</t>
+          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsInvestingActivities</t>
         </is>
       </c>
       <c r="D9" s="35" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E9" s="35" t="n">
-        <v>21000</v>
+        <v>3000</v>
       </c>
       <c r="F9" s="35" t="n">
-        <v>113000</v>
+        <v>-14000</v>
       </c>
       <c r="G9" s="35" t="n">
-        <v>43000</v>
+        <v>-7000</v>
       </c>
       <c r="H9" s="35" t="n">
-        <v>121000</v>
+        <v>-22000</v>
       </c>
       <c r="I9" s="36" t="inlineStr">
         <is>
@@ -7363,29 +7619,23 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialAssets</t>
+          <t>ifrs-full:ProceedsFromExerciseOfOptions</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialAssets</t>
+          <t>ifrs-full:ProceedsFromExerciseOfOptions</t>
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>36000</v>
+        <v>48000</v>
       </c>
       <c r="E10" s="38" t="n">
-        <v>299000</v>
-      </c>
-      <c r="F10" s="38" t="n">
-        <v>155000</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>113000</v>
-      </c>
-      <c r="H10" s="38" t="n">
-        <v>69000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="38" t="n"/>
+      <c r="H10" s="38" t="n"/>
       <c r="I10" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7400,28 +7650,24 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialLiabilities</t>
+          <t>ifrs-full:ProceedsFromIssueOfBondsNotesAndDebentures</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialLiabilities</t>
-        </is>
-      </c>
-      <c r="D11" s="35" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E11" s="35" t="n">
-        <v>8000</v>
-      </c>
+          <t>ifrs-full:ProceedsFromIssueOfBondsNotesAndDebentures</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
       <c r="F11" s="35" t="n">
-        <v>43000</v>
+        <v>981000</v>
       </c>
       <c r="G11" s="35" t="n">
-        <v>74000</v>
+        <v>1203000</v>
       </c>
       <c r="H11" s="35" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="I11" s="36" t="inlineStr">
         <is>
@@ -7437,27 +7683,27 @@
       </c>
       <c r="B12" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentPrepayments</t>
+          <t>ifrs-full:RepaymentsOfBondsNotesAndDebentures</t>
         </is>
       </c>
       <c r="C12" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentPrepayments</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="n">
-        <v>222000</v>
-      </c>
+          <t>ifrs-full:RepaymentsOfBondsNotesAndDebentures</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="n"/>
       <c r="E12" s="38" t="n">
-        <v>124000</v>
+        <v>1000000</v>
       </c>
       <c r="F12" s="38" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="38" t="n">
+        <v>305000</v>
+      </c>
+      <c r="H12" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="38" t="n"/>
       <c r="I12" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7472,21 +7718,27 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:OtherCashPaymentsToAcquireEquityOrDebtInstrumentsOfOtherEntitiesClassifiedAsInvestingActivities</t>
+          <t>ifrs-full:RestrictedCashAndCashEquivalents</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:OtherCashPaymentsToAcquireEquityOrDebtInstrumentsOfOtherEntitiesClassifiedAsInvestingActivities</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n">
-        <v>280000</v>
-      </c>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
+          <t>ifrs-full:RestrictedCashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>167000</v>
+      </c>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G13" s="35" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>18000</v>
+      </c>
       <c r="I13" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7501,28 +7753,24 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsFinancingActivities</t>
+          <t>ifrs-full:ReversalOfImpairmentLossRecognisedInProfitOrLoss</t>
         </is>
       </c>
       <c r="C14" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsFinancingActivities</t>
-        </is>
-      </c>
-      <c r="D14" s="38" t="n">
+          <t>ifrs-full:ReversalOfImpairmentLossRecognisedInProfitOrLoss</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="38" t="n">
-        <v>-33000</v>
-      </c>
-      <c r="F14" s="38" t="n">
-        <v>-8000</v>
-      </c>
       <c r="G14" s="38" t="n">
-        <v>-6000</v>
+        <v>33000</v>
       </c>
       <c r="H14" s="38" t="n">
-        <v>41000</v>
+        <v>0</v>
       </c>
       <c r="I14" s="39" t="inlineStr">
         <is>
@@ -7538,234 +7786,30 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsInvestingActivities</t>
+          <t>ifrs-full:Ships</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsInvestingActivities</t>
+          <t>ifrs-full:Ships</t>
         </is>
       </c>
       <c r="D15" s="35" t="n">
-        <v>1000</v>
+        <v>11460000</v>
       </c>
       <c r="E15" s="35" t="n">
-        <v>3000</v>
+        <v>13186000</v>
       </c>
       <c r="F15" s="35" t="n">
-        <v>-14000</v>
+        <v>11782000</v>
       </c>
       <c r="G15" s="35" t="n">
-        <v>-7000</v>
+        <v>11712000</v>
       </c>
       <c r="H15" s="35" t="n">
-        <v>-22000</v>
+        <v>11106000</v>
       </c>
       <c r="I15" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromExerciseOfOptions</t>
-        </is>
-      </c>
-      <c r="C16" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromExerciseOfOptions</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="n">
-        <v>48000</v>
-      </c>
-      <c r="E16" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="38" t="n"/>
-      <c r="G16" s="38" t="n"/>
-      <c r="H16" s="38" t="n"/>
-      <c r="I16" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromIssueOfBondsNotesAndDebentures</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromIssueOfBondsNotesAndDebentures</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n">
-        <v>981000</v>
-      </c>
-      <c r="G17" s="35" t="n">
-        <v>1203000</v>
-      </c>
-      <c r="H17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:RepaymentsOfBondsNotesAndDebentures</t>
-        </is>
-      </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:RepaymentsOfBondsNotesAndDebentures</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="38" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F18" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="38" t="n">
-        <v>305000</v>
-      </c>
-      <c r="H18" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:RestrictedCashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:RestrictedCashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="n">
-        <v>167000</v>
-      </c>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n">
-        <v>14000</v>
-      </c>
-      <c r="G19" s="35" t="n">
-        <v>11000</v>
-      </c>
-      <c r="H19" s="35" t="n">
-        <v>18000</v>
-      </c>
-      <c r="I19" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B20" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ReversalOfImpairmentLossRecognisedInProfitOrLoss</t>
-        </is>
-      </c>
-      <c r="C20" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ReversalOfImpairmentLossRecognisedInProfitOrLoss</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="38" t="n"/>
-      <c r="F20" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="38" t="n">
-        <v>33000</v>
-      </c>
-      <c r="H20" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:Ships</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:Ships</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="n">
-        <v>11460000</v>
-      </c>
-      <c r="E21" s="35" t="n">
-        <v>13186000</v>
-      </c>
-      <c r="F21" s="35" t="n">
-        <v>11782000</v>
-      </c>
-      <c r="G21" s="35" t="n">
-        <v>11712000</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>11106000</v>
-      </c>
-      <c r="I21" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/14194711_dfds.xlsx
+++ b/filer/14194711_dfds.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4674,6 +4675,148 @@
       </c>
       <c r="F96" s="13">
         <f>IFERROR($F$36/($F$58+$F$65)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B99" s="17">
+        <f>'pengestrom_raw'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C99" s="17">
+        <f>'pengestrom_raw'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D99" s="17">
+        <f>'pengestrom_raw'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E99" s="17">
+        <f>'pengestrom_raw'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F99" s="17">
+        <f>'pengestrom_raw'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B100" s="17">
+        <f>'pengestrom_raw'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C100" s="17">
+        <f>'pengestrom_raw'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D100" s="17">
+        <f>'pengestrom_raw'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E100" s="17">
+        <f>'pengestrom_raw'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F100" s="17">
+        <f>'pengestrom_raw'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B101" s="17">
+        <f>'pengestrom_raw'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C101" s="17">
+        <f>'pengestrom_raw'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D101" s="17">
+        <f>'pengestrom_raw'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E101" s="17">
+        <f>'pengestrom_raw'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F101" s="17">
+        <f>'pengestrom_raw'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B103">
+        <f>IF(ABS(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C103">
+        <f>IF(ABS(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D103">
+        <f>IF(ABS(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E103">
+        <f>IF(ABS(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F103">
+        <f>IF(ABS(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4722,347 +4865,347 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>17869000</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>26873000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>27304000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>29753000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>30947000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>21000</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>113000</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>43000</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>240000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>643000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>1015000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>1206000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>1424000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>1423000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>3444000</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>4730000</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>5572000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>6361000</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>7117000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>2087000</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>2505000</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>2473000</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>2793000</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>3108000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>1348000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>2482000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>2326000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>1506000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>520000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>-13000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>-14000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>-26000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>-9000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>-8000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>29000</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>66000</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>80000</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>47000</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>38000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>307000</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>409000</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>739000</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>870000</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>856000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>1069000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>2139000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>1667000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>683000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>-298000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>94000</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>120000</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>148000</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>142000</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>127000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>976000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>2019000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>1519000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>541000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>-425000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5109,960 +5252,960 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>599000</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>676000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>831000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>755000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>677000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>4280000</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>4407000</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>4952000</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>7497000</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>7631000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>6252000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>6444000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>7136000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>9837000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>9825000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>427000</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>559000</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>759000</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>828000</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>823000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>1289000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>1600000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>1939000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>2531000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>2403000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>35000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>13000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="F12" s="16" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>366000</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>500000</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>238000</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>225000</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>150000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>25807000</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>28141000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>28691000</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>31996000</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>30507000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>269000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>324000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>339000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>322000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>255000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>3423000</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>4015000</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>4459000</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>4871000</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>4080000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>171000</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>223000</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>251000</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>218000</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>238000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>299000</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>368000</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>400000</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>452000</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="17" t="n">
         <v>447000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>31000</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>49000</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>79000</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>82000</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>74000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>902000</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>1189000</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>737000</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>1589000</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <v>1795000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>4914000</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>5943000</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>5956000</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>7286000</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <v>6610000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>30721000</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>34084000</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>34647000</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>39281000</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>37117000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>1173000</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>1173000</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>1173000</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>1159000</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>1124000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>-396000</v>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>-284000</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>-451000</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>-490000</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>-446000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>10435000</v>
       </c>
-      <c r="C34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>12133000</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>13119000</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>13145000</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="F34" s="17" t="n">
         <v>12693000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>11446000</v>
       </c>
-      <c r="C35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>13022000</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>13840000</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>13814000</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="17" t="n">
         <v>13371000</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>366000</v>
       </c>
-      <c r="C36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>359000</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>468000</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>522000</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="17" t="n">
         <v>550000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>76000</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>88000</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>90000</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>104000</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>123000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
+      <c r="B41" s="17" t="n">
         <v>6000</v>
       </c>
-      <c r="C41" s="16" t="n">
+      <c r="C41" s="17" t="n">
         <v>8000</v>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="17" t="n">
         <v>43000</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="17" t="n">
         <v>74000</v>
       </c>
-      <c r="F41" s="16" t="n">
+      <c r="F41" s="17" t="n">
         <v>40000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>11825000</v>
       </c>
-      <c r="C42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>12397000</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>13602000</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <v>17113000</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="17" t="n">
         <v>14477000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
+      <c r="B45" s="17" t="n">
         <v>2511000</v>
       </c>
-      <c r="C45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>3137000</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>1627000</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>1621000</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F45" s="17" t="n">
         <v>2539000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>3119000</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>3661000</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>3461000</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>3984000</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="17" t="n">
         <v>3753000</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n"/>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="17" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
+      <c r="B52" s="17" t="n">
         <v>730000</v>
       </c>
-      <c r="C52" s="16" t="n">
+      <c r="C52" s="17" t="n">
         <v>768000</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D52" s="17" t="n">
         <v>904000</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="E52" s="17" t="n">
         <v>1160000</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="F52" s="17" t="n">
         <v>1135000</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="n"/>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="16" t="n"/>
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n"/>
+      <c r="F53" s="17" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
+      <c r="B54" s="17" t="n">
         <v>6778000</v>
       </c>
-      <c r="C54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>8053000</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>6491000</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="E54" s="17" t="n">
         <v>7521000</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="F54" s="17" t="n">
         <v>8421000</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>19167000</v>
       </c>
-      <c r="C55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>20949000</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>20715000</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>25392000</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="F55" s="17" t="n">
         <v>23670000</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n">
+      <c r="B56" s="17" t="n">
         <v>30721000</v>
       </c>
-      <c r="C56" s="16" t="n">
+      <c r="C56" s="17" t="n">
         <v>34084000</v>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="D56" s="17" t="n">
         <v>34647000</v>
       </c>
-      <c r="E56" s="16" t="n">
+      <c r="E56" s="17" t="n">
         <v>39281000</v>
       </c>
-      <c r="F56" s="16" t="n">
+      <c r="F56" s="17" t="n">
         <v>37117000</v>
       </c>
     </row>
@@ -6072,6 +6215,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>3208000</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>4480000</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>3675000</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>3420000</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>3300000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-3210000</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-2989000</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-1149000</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-3647000</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-342000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-359000</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-1203000</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-2980000</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>1075000</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-2742000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7294,7 +7559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
